--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-05-2025.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.98</t>
+          <t>£11.18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£13.33</t>
+          <t>£12.83</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£17.00</t>
+          <t>£14.46</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£17.50</t>
+          <t>£16.74</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.44</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£24.60</t>
+          <t>£23.15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£24.00</t>
+          <t>£23.49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£27.00</t>
+          <t>£26.78</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£30.50</t>
+          <t>£29.31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£29.50</t>
+          <t>£28.60</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£35.08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£42.78</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£48.12</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£730.00</t>
+          <t>£734.81</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£940.00</t>
+          <t>£915.40</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£33.20</t>
+          <t>£29.79</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£39.91</t>
+          <t>£36.73</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£45.89</t>
+          <t>£39.88</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£52.00</t>
+          <t>£44.50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£45.50</t>
+          <t>£45.19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£48.82</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>£44.78</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>£45.00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>£55.89</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>£45.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>£55.89</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>£45.00</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>£58.00</t>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£67.41</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£1,173.28</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,225.00</t>
+          <t>£1,213.28</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
